--- a/data/dividends_info_20260821.xlsx
+++ b/data/dividends_info_20260821.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.72499847412109</v>
+        <v>43.08000183105469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2058319111280634</v>
+        <v>0.2089136401454898</v>
       </c>
       <c r="J2" t="n">
         <v>206</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.25</v>
+        <v>66.80000305175781</v>
       </c>
       <c r="I3" t="n">
-        <v>1.056603773584906</v>
+        <v>1.047904143743269</v>
       </c>
       <c r="J3" t="n">
         <v>185</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4779999852180481</v>
+        <v>0.4819999933242798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8368201095603234</v>
+        <v>0.8298755301660101</v>
       </c>
       <c r="J5" t="n">
         <v>115</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.70500183105469</v>
+        <v>43.08000183105469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2059260867849919</v>
+        <v>0.2089136401454898</v>
       </c>
       <c r="J6" t="n">
         <v>115</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.095000028610229</v>
+        <v>2.109999895095825</v>
       </c>
       <c r="I7" t="n">
-        <v>3.675417610904753</v>
+        <v>3.649289280960038</v>
       </c>
       <c r="J7" t="n">
         <v>94</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24.59000015258789</v>
+        <v>24.13999938964844</v>
       </c>
       <c r="I8" t="n">
-        <v>1.098007313235355</v>
+        <v>1.118475587517122</v>
       </c>
       <c r="J8" t="n">
         <v>94</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22.61000061035156</v>
+        <v>22.3700008392334</v>
       </c>
       <c r="I9" t="n">
-        <v>2.609464768125126</v>
+        <v>2.637460786166957</v>
       </c>
       <c r="J9" t="n">
         <v>94</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.809999942779541</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="I10" t="n">
-        <v>3.442340825640675</v>
+        <v>3.460207486854598</v>
       </c>
       <c r="J10" t="n">
         <v>87</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.39999961853027</v>
+        <v>10.52999973297119</v>
       </c>
       <c r="I11" t="n">
-        <v>4.423077085314424</v>
+        <v>4.368471145917155</v>
       </c>
       <c r="J11" t="n">
         <v>66</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.599999904632568</v>
+        <v>7.650000095367432</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7894736941171157</v>
+        <v>0.7843137157126817</v>
       </c>
       <c r="J12" t="n">
         <v>59</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4779999852180481</v>
+        <v>0.4819999933242798</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8368201095603234</v>
+        <v>0.8298755301660101</v>
       </c>
       <c r="J13" t="n">
         <v>59</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.989999771118164</v>
+        <v>1.25</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7615230810218038</v>
+        <v>3.04</v>
       </c>
       <c r="J15" t="n">
         <v>38</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>24.59000015258789</v>
+        <v>24.13999938964844</v>
       </c>
       <c r="I16" t="n">
-        <v>1.098007313235355</v>
+        <v>1.118475587517122</v>
       </c>
       <c r="J16" t="n">
         <v>31</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.022000074386597</v>
+        <v>2.046000003814697</v>
       </c>
       <c r="I17" t="n">
-        <v>2.818990994216051</v>
+        <v>2.78592374847143</v>
       </c>
       <c r="J17" t="n">
         <v>31</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>43.70500183105469</v>
+        <v>43.08000183105469</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2059260867849919</v>
+        <v>0.2089136401454898</v>
       </c>
       <c r="J18" t="n">
         <v>31</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>89.59999847412109</v>
+        <v>89.94999694824219</v>
       </c>
       <c r="I19" t="n">
-        <v>1.484375025278756</v>
+        <v>1.478599271954718</v>
       </c>
       <c r="J19" t="n">
         <v>31</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.820000171661377</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I20" t="n">
-        <v>5.154639023221232</v>
+        <v>5.050505001853162</v>
       </c>
       <c r="J20" t="n">
         <v>24</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4779999852180481</v>
+        <v>0.4819999933242798</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8368201095603234</v>
+        <v>0.8298755301660101</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.019999980926514</v>
+        <v>1.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7569721144298999</v>
+        <v>3.04</v>
       </c>
       <c r="J23" t="n">
         <v>-18</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.519999980926514</v>
+        <v>2.529999971389771</v>
       </c>
       <c r="I25" t="n">
-        <v>5.871785758728343</v>
+        <v>5.848577141236812</v>
       </c>
       <c r="J25" t="n">
         <v>-18</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.940000057220459</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="I26" t="n">
-        <v>4.208754168210969</v>
+        <v>4.215851724063898</v>
       </c>
       <c r="J26" t="n">
         <v>-25</v>
